--- a/diagrams/juryFull/JuryFull.xlsx
+++ b/diagrams/juryFull/JuryFull.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms-firmata\diagrams\juryFull\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1CBD9F-CB26-49E6-A990-84F1D159886C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAE6BA3-4A95-450F-B780-99E77FF1C600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9C8F068-60C0-4FDD-8C1E-880F519290ED}"/>
   </bookViews>
@@ -48,15 +48,9 @@
     <t>ON</t>
   </si>
   <si>
-    <t>fop/resetDecisions/A</t>
-  </si>
-  <si>
     <t>OFF</t>
   </si>
   <si>
-    <t>fop/startup/A</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -78,15 +72,9 @@
     <t>pin action</t>
   </si>
   <si>
-    <t>fop/decision/A</t>
-  </si>
-  <si>
     <t>1 hidden</t>
   </si>
   <si>
-    <t>fop/juryMemberDecision/A</t>
-  </si>
-  <si>
     <t>Ref 1 Summon</t>
   </si>
   <si>
@@ -543,16 +531,28 @@
     <t>Resume Competition</t>
   </si>
   <si>
-    <t>owlcms/fop/juryDeliberation/A</t>
-  </si>
-  <si>
     <t>Challenge</t>
   </si>
   <si>
     <t>challenge</t>
   </si>
   <si>
-    <t>owlcms/fop/challenge/A</t>
+    <t>fop/resetDecisions</t>
+  </si>
+  <si>
+    <t>fop/startup</t>
+  </si>
+  <si>
+    <t>fop/decision</t>
+  </si>
+  <si>
+    <t>fop/juryMemberDecision</t>
+  </si>
+  <si>
+    <t>owlcms/fop/juryDeliberation</t>
+  </si>
+  <si>
+    <t>owlcms/fop/challenge</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1011,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1020,27 +1020,27 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -1049,15 +1049,15 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -1066,15 +1066,15 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B4">
         <v>21</v>
@@ -1083,15 +1083,15 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -1100,15 +1100,15 @@
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>19</v>
@@ -1117,15 +1117,15 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>18</v>
@@ -1134,15 +1134,15 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B8">
         <v>17</v>
@@ -1151,63 +1151,63 @@
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B9" s="9">
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B10" s="9">
         <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B11" s="9">
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B12" s="10">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -1218,13 +1218,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B13" s="10">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>3</v>
@@ -1235,13 +1235,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B14" s="10">
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1252,16 +1252,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B15" s="10">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>3</v>
@@ -1269,50 +1269,50 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="10">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B17" s="10">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B18" s="10">
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
@@ -1320,16 +1320,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B19" s="10">
         <v>12</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>3</v>
@@ -1337,16 +1337,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="10">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B21" s="8">
         <v>10</v>
@@ -1364,7 +1364,7 @@
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
@@ -1372,55 +1372,55 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B22" s="9">
         <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B23" s="9">
         <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B24" s="9">
         <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>3</v>
@@ -1431,13 +1431,13 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>3</v>
@@ -1448,13 +1448,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B27" s="5">
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>3</v>
@@ -1465,16 +1465,16 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B28" s="5">
         <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>3</v>
@@ -1482,50 +1482,50 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B29" s="5">
         <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B30" s="5">
         <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B31" s="5">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>3</v>
@@ -1533,16 +1533,16 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5">
         <v>8</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -1550,16 +1550,16 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5">
         <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>3</v>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B34" s="8">
         <v>6</v>
@@ -1577,7 +1577,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I34" s="2">
         <v>2</v>
@@ -1585,55 +1585,55 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B35" s="9">
         <v>5</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B36" s="9">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B37" s="9">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B38" s="5">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>3</v>
@@ -1641,13 +1641,13 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B39" s="5">
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>3</v>
@@ -1655,13 +1655,13 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B40" s="5">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>3</v>
@@ -1669,16 +1669,16 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B41" s="5">
         <v>5</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>3</v>
@@ -1686,50 +1686,50 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B42" s="5">
         <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B43" s="5">
         <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B44" s="5">
         <v>5</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -1737,16 +1737,16 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B45" s="5">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B46" s="5">
         <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>3</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B47" s="8">
         <v>2</v>
@@ -1781,7 +1781,7 @@
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I47" s="2">
         <v>3</v>
@@ -1789,13 +1789,13 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B48" s="9">
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="3" t="s">
@@ -1807,13 +1807,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B49" s="9">
         <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="3" t="s">
@@ -1825,13 +1825,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B50" s="9">
         <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="3" t="s">
@@ -1843,33 +1843,33 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B51" s="5">
         <v>25</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B52" s="5">
         <v>27</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -1877,33 +1877,33 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B53" s="5">
         <v>29</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B54" s="5">
         <v>25</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>3</v>
@@ -1911,50 +1911,50 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B55" s="5">
         <v>27</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B56" s="5">
         <v>29</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B57" s="5">
         <v>25</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
@@ -1962,16 +1962,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B58" s="5">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
@@ -1979,16 +1979,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B59" s="5">
         <v>29</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -1996,91 +1996,91 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B60" s="5">
         <v>25</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B61" s="5">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B62" s="5">
         <v>29</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B63" s="5">
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B64" s="5">
         <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B65" s="5">
         <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B66" s="5">
         <v>25</v>
@@ -2089,12 +2089,12 @@
         <v>172</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B67" s="5">
         <v>27</v>
@@ -2103,12 +2103,12 @@
         <v>172</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B68" s="5">
         <v>29</v>
@@ -2117,12 +2117,12 @@
         <v>172</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B69" s="4">
         <v>62</v>
@@ -2132,15 +2132,15 @@
         <v>3</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B70" s="4">
         <v>63</v>
@@ -2150,21 +2150,21 @@
         <v>3</v>
       </c>
       <c r="H70" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B71" s="9">
         <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="3" t="s">
@@ -2176,13 +2176,13 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B72" s="9">
         <v>33</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="3" t="s">
@@ -2194,13 +2194,13 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B73" s="9">
         <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D73" s="7"/>
       <c r="E73" s="3" t="s">
@@ -2212,33 +2212,33 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B74" s="5">
         <v>31</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B75" s="5">
         <v>33</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>3</v>
@@ -2246,33 +2246,33 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B76" s="5">
         <v>35</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B77" s="5">
         <v>31</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>3</v>
@@ -2280,50 +2280,50 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B78" s="5">
         <v>33</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B79" s="5">
         <v>35</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B80" s="5">
         <v>31</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>3</v>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B81" s="5">
         <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D81" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>3</v>
@@ -2348,16 +2348,16 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B82" s="5">
         <v>35</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>3</v>
@@ -2365,91 +2365,91 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B83" s="5">
         <v>31</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B84" s="5">
         <v>33</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B85" s="5">
         <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B86" s="5">
         <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B87" s="5">
         <v>33</v>
       </c>
       <c r="C87" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B88" s="5">
         <v>35</v>
       </c>
       <c r="C88" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B89" s="5">
         <v>31</v>
@@ -2458,12 +2458,12 @@
         <v>172</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B90" s="5">
         <v>33</v>
@@ -2472,12 +2472,12 @@
         <v>172</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B91" s="5">
         <v>35</v>
@@ -2486,12 +2486,12 @@
         <v>172</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B92" s="4">
         <v>60</v>
@@ -2501,15 +2501,15 @@
         <v>3</v>
       </c>
       <c r="H92" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B93" s="4">
         <v>61</v>
@@ -2519,21 +2519,21 @@
         <v>3</v>
       </c>
       <c r="H93" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B94" s="9">
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="3" t="s">
@@ -2545,13 +2545,13 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B95" s="9">
         <v>39</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="3" t="s">
@@ -2563,13 +2563,13 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B96" s="9">
         <v>41</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="3" t="s">
@@ -2581,33 +2581,33 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B97" s="5">
         <v>37</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B98" s="5">
         <v>39</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>3</v>
@@ -2615,33 +2615,33 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B99" s="5">
         <v>41</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B100" s="5">
         <v>37</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -2649,50 +2649,50 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B101" s="5">
         <v>39</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B102" s="5">
         <v>41</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B103" s="5">
         <v>37</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>3</v>
@@ -2700,16 +2700,16 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B104" s="5">
         <v>39</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D104" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>3</v>
@@ -2717,16 +2717,16 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B105" s="5">
         <v>41</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D105" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>3</v>
@@ -2734,91 +2734,91 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B106" s="5">
         <v>37</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B107" s="5">
         <v>39</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B108" s="5">
         <v>41</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B109" s="5">
         <v>37</v>
       </c>
       <c r="C109" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B110" s="5">
         <v>39</v>
       </c>
       <c r="C110" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B111" s="5">
         <v>41</v>
       </c>
       <c r="C111" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B112" s="5">
         <v>37</v>
@@ -2827,12 +2827,12 @@
         <v>172</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B113" s="5">
         <v>39</v>
@@ -2841,12 +2841,12 @@
         <v>172</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B114" s="5">
         <v>41</v>
@@ -2855,12 +2855,12 @@
         <v>172</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B115" s="4">
         <v>58</v>
@@ -2870,15 +2870,15 @@
         <v>3</v>
       </c>
       <c r="H115" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B116" s="4">
         <v>59</v>
@@ -2888,21 +2888,21 @@
         <v>3</v>
       </c>
       <c r="H116" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B117" s="9">
         <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="3" t="s">
@@ -2914,13 +2914,13 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B118" s="9">
         <v>45</v>
       </c>
       <c r="C118" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="3" t="s">
@@ -2932,13 +2932,13 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B119" s="9">
         <v>47</v>
       </c>
       <c r="C119" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="3" t="s">
@@ -2950,33 +2950,33 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B120" s="5">
         <v>43</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B121" s="5">
         <v>45</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>3</v>
@@ -2984,33 +2984,33 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B122" s="5">
         <v>47</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B123" s="5">
         <v>43</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>3</v>
@@ -3018,50 +3018,50 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B124" s="5">
         <v>45</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B125" s="5">
         <v>47</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B126" s="5">
         <v>43</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>3</v>
@@ -3069,16 +3069,16 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B127" s="5">
         <v>45</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D127" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>3</v>
@@ -3086,16 +3086,16 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B128" s="5">
         <v>47</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D128" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>3</v>
@@ -3103,91 +3103,91 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B129" s="5">
         <v>43</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B130" s="5">
         <v>45</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B131" s="5">
         <v>47</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B132" s="5">
         <v>43</v>
       </c>
       <c r="C132" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B133" s="5">
         <v>45</v>
       </c>
       <c r="C133" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B134" s="5">
         <v>47</v>
       </c>
       <c r="C134" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B135" s="5">
         <v>43</v>
@@ -3196,12 +3196,12 @@
         <v>172</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B136" s="5">
         <v>45</v>
@@ -3210,12 +3210,12 @@
         <v>172</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B137" s="5">
         <v>47</v>
@@ -3224,12 +3224,12 @@
         <v>172</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B138" s="4">
         <v>56</v>
@@ -3239,15 +3239,15 @@
         <v>3</v>
       </c>
       <c r="H138" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B139" s="4">
         <v>57</v>
@@ -3257,21 +3257,21 @@
         <v>3</v>
       </c>
       <c r="H139" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B140" s="9">
         <v>49</v>
       </c>
       <c r="C140" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="3" t="s">
@@ -3283,13 +3283,13 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B141" s="9">
         <v>51</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="3" t="s">
@@ -3301,13 +3301,13 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B142" s="9">
         <v>53</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="3" t="s">
@@ -3319,33 +3319,33 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B143" s="5">
         <v>49</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B144" s="5">
         <v>51</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>3</v>
@@ -3353,33 +3353,33 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B145" s="5">
         <v>53</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B146" s="5">
         <v>49</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>3</v>
@@ -3387,50 +3387,50 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B147" s="5">
         <v>51</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B148" s="5">
         <v>53</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B149" s="5">
         <v>49</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>3</v>
@@ -3438,16 +3438,16 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B150" s="5">
         <v>51</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D150" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>3</v>
@@ -3455,16 +3455,16 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B151" s="5">
         <v>53</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="D151" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>3</v>
@@ -3472,91 +3472,91 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B152" s="5">
         <v>49</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B153" s="5">
         <v>51</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B154" s="5">
         <v>53</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B155" s="5">
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B156" s="5">
         <v>51</v>
       </c>
       <c r="C156" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B157" s="5">
         <v>53</v>
       </c>
       <c r="C157" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B158" s="5">
         <v>49</v>
@@ -3565,12 +3565,12 @@
         <v>172</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B159" s="5">
         <v>51</v>
@@ -3579,12 +3579,12 @@
         <v>172</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B160" s="5">
         <v>53</v>
@@ -3593,12 +3593,12 @@
         <v>172</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B161" s="4">
         <v>54</v>
@@ -3608,15 +3608,15 @@
         <v>3</v>
       </c>
       <c r="H161" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B162" s="4">
         <v>55</v>
@@ -3626,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="H162" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
